--- a/Annexe - Bloc1-Tableau de synthèse -.xlsx
+++ b/Annexe - Bloc1-Tableau de synthèse -.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Centre de formation :</t>
   </si>
   <si>
-    <t>▢ SISR</t>
-  </si>
-  <si>
     <t>▢ SLAM</t>
   </si>
   <si>
@@ -115,15 +112,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
-    <t>SESSION 202x</t>
-  </si>
-  <si>
-    <t>NOM et prénom : thomas</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -134,6 +122,27 @@
   </si>
   <si>
     <t>https://thomas-iniguez-visioli.github.io/2026/01/26/PREFSUP_DESCRIPTION/</t>
+  </si>
+  <si>
+    <t>x SISR</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOM et prénom : thomas iniguez visioli </t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio :  https://thomas-iniguez-visioli.github.io/</t>
+  </si>
+  <si>
+    <t>https://thomas-iniguez-visioli.github.io/2026/01/26/vbcq_volley_repos/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thomas-iniguez-visioli.github.io/2026/01/26/vbcq_volley_repos/  non mis en production faute de réponse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf avant après vbcq </t>
   </si>
 </sst>
 </file>
@@ -143,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -205,6 +214,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -601,11 +616,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -670,15 +686,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -712,33 +752,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Euro" xfId="1"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1055,84 +1075,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="24"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="43"/>
+      <c r="A3" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="24"/>
+      <c r="H3" s="30"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="A5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>21</v>
+      <c r="A6" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1154,8 +1174,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1211,16 +1231,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="A8" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1708,16 +1728,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="A19" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="38"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1755,10 +1775,12 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="B20" s="10"/>
       <c r="C20" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -1802,11 +1824,13 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="B21" s="10"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
@@ -1849,12 +1873,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+      <c r="A22" s="44" t="s">
+        <v>32</v>
+      </c>
       <c r="B22" s="10"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
@@ -1903,7 +1929,7 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23"/>
@@ -2078,16 +2104,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="A27" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2125,13 +2151,15 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="B28" s="10"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="18"/>
@@ -2173,15 +2201,17 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29"/>
@@ -2222,7 +2252,7 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="17"/>
@@ -2231,7 +2261,7 @@
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -2542,11 +2572,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2554,8 +2579,16 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A22" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait"/>

--- a/Annexe - Bloc1-Tableau de synthèse -.xlsx
+++ b/Annexe - Bloc1-Tableau de synthèse -.xlsx
@@ -85,9 +85,6 @@
 ▸Développer son projet professionnel</t>
   </si>
   <si>
-    <t>Centre de formation :</t>
-  </si>
-  <si>
     <t>▢ SLAM</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -143,6 +137,12 @@
   </si>
   <si>
     <t xml:space="preserve">cf avant après vbcq </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre de formation : lycée chaptal quimper </t>
+  </si>
+  <si>
+    <t>N° candidat : 02147212582</t>
   </si>
 </sst>
 </file>
@@ -686,9 +686,51 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -712,48 +754,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1075,84 +1075,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="A3" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="A5" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1174,8 +1174,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1231,16 +1231,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="A8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1728,16 +1728,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="A19" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1776,11 +1776,11 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -1825,12 +1825,12 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
@@ -1873,14 +1873,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="44" t="s">
-        <v>32</v>
+      <c r="A22" s="22" t="s">
+        <v>30</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
@@ -1929,7 +1929,7 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23"/>
@@ -2104,16 +2104,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
+      <c r="A27" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2152,14 +2152,14 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="18"/>
@@ -2201,17 +2201,17 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29"/>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="17"/>
@@ -2261,7 +2261,7 @@
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -2572,6 +2572,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2579,11 +2584,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/Annexe - Bloc1-Tableau de synthèse -.xlsx
+++ b/Annexe - Bloc1-Tableau de synthèse -.xlsx
@@ -689,15 +689,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -729,30 +753,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1075,56 +1075,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="43" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="31"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1136,22 +1136,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="40" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1174,8 +1174,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1231,16 +1231,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1728,16 +1728,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="31"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1778,7 +1778,9 @@
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="10"/>
+      <c r="B20" s="10">
+        <v>2025</v>
+      </c>
       <c r="C20" s="17" t="s">
         <v>21</v>
       </c>
@@ -2104,16 +2106,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2203,7 +2205,9 @@
       <c r="A29" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="10"/>
+      <c r="B29" s="10">
+        <v>2026</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
         <v>21</v>
@@ -2572,11 +2576,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2584,6 +2583,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -2591,7 +2595,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/Annexe - Bloc1-Tableau de synthèse -.xlsx
+++ b/Annexe - Bloc1-Tableau de synthèse -.xlsx
@@ -621,7 +621,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -689,9 +689,48 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -716,44 +755,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1075,56 +1078,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="23"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="30" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="31"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1136,22 +1139,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1174,8 +1177,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1231,16 +1234,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1728,16 +1731,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1781,7 +1784,7 @@
       <c r="B20" s="10">
         <v>2025</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="45" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="17"/>
@@ -1831,7 +1834,7 @@
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="45" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="17"/>
@@ -1881,7 +1884,7 @@
       <c r="B22" s="10"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="45" t="s">
         <v>22</v>
       </c>
       <c r="F22" s="17"/>
@@ -1930,7 +1933,7 @@
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="45" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="18"/>
@@ -2106,16 +2109,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2160,7 +2163,7 @@
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="45" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="17"/>
@@ -2209,12 +2212,12 @@
         <v>2026</v>
       </c>
       <c r="C29" s="17"/>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="45" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="45" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="18"/>
@@ -2264,7 +2267,7 @@
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
-      <c r="H30" s="18" t="s">
+      <c r="H30" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I30"/>
@@ -2576,6 +2579,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2583,11 +2591,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
